--- a/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
@@ -18,8 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="19">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,6 +126,11 @@
       <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -201,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -213,6 +220,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -264,6 +274,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -640,8 +653,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -2855,23 +2868,19 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>12592000</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>21525</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2880,12 +2889,12 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2895,7 +2904,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3695,23 +3704,19 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>12114000</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>20708</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3720,12 +3725,12 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -3735,7 +3740,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6215,23 +6220,19 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>11276000</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>19275</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6240,12 +6241,12 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -6255,7 +6256,7 @@
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -9925,23 +9926,19 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I134" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>10996000</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>18296</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -9950,12 +9947,12 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M134" s="3" t="inlineStr">
@@ -9965,7 +9962,7 @@
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18815,110 +18812,110 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>1A座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -18926,7 +18923,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -18934,7 +18931,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 868呎 (3房)
 -
@@ -18942,15 +18939,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -18958,7 +18955,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -18966,7 +18963,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 868呎 (3房)
 -
@@ -18974,15 +18971,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -18990,7 +18987,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -18998,7 +18995,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19006,7 +19003,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19016,12 +19013,12 @@
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19029,7 +19026,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19037,7 +19034,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19045,7 +19042,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19055,12 +19052,12 @@
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19068,7 +19065,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19076,7 +19073,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19084,7 +19081,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19094,12 +19091,12 @@
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19107,7 +19104,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19115,7 +19112,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19123,7 +19120,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19133,12 +19130,12 @@
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19146,7 +19143,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19154,7 +19151,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19162,7 +19159,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19172,12 +19169,12 @@
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19185,7 +19182,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19193,7 +19190,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19201,7 +19198,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19211,12 +19208,12 @@
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19224,7 +19221,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19232,7 +19229,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19240,7 +19237,46 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 585呎 (2房)
+$1259万
+$21,525/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1395呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 601呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19249,13 +19285,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19263,7 +19299,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19271,7 +19307,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19279,7 +19315,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19288,13 +19324,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19302,7 +19338,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19310,7 +19346,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19318,7 +19354,46 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 585呎 (2房)
+$1211万
+$20,708/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1395呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 601呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19327,13 +19402,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19341,7 +19416,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19349,7 +19424,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19357,7 +19432,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19366,13 +19441,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19380,7 +19455,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19388,7 +19463,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19396,7 +19471,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19405,13 +19480,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19419,7 +19494,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19427,7 +19502,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19435,7 +19510,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19444,13 +19519,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19458,7 +19533,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19466,7 +19541,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19474,7 +19549,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19483,13 +19558,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19497,7 +19572,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19505,7 +19580,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19513,7 +19588,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19522,13 +19597,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19536,7 +19611,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19544,7 +19619,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19552,7 +19627,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19561,13 +19636,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19575,7 +19650,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19583,7 +19658,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 -
@@ -19591,7 +19666,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19600,13 +19675,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19614,7 +19689,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19622,15 +19697,54 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>D | 585呎 (2房)
+$1128万
+$19,275/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 784呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 601呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19639,13 +19753,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 1395呎 (4+房)
 -
@@ -19653,7 +19767,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 784呎 (3房)
 -
@@ -19661,15 +19775,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19678,29 +19792,29 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 1395呎 (4+房)
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 784呎 (3房)
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 招标单位
@@ -19708,7 +19822,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19717,29 +19831,29 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 1395呎 (4+房)
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>B | 784呎 (3房)
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 招标单位
@@ -19747,7 +19861,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19756,29 +19870,29 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 1395呎 (4+房)
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 784呎 (3房)
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 招标单位
@@ -19786,7 +19900,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19795,13 +19909,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 1393呎 (4+房)
 -
@@ -19809,7 +19923,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 786呎 (3房)
 -
@@ -19817,7 +19931,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 招标单位
@@ -19825,7 +19939,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19834,13 +19948,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 1393呎 (4+房)
 -
@@ -19848,7 +19962,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 786呎 (3房)
 -
@@ -19856,7 +19970,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 招标单位
@@ -19864,7 +19978,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19873,13 +19987,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 1393呎 (4+房)
 -
@@ -19887,7 +20001,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 786呎 (3房)
 -
@@ -19895,7 +20009,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 招标单位
@@ -19903,7 +20017,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19912,13 +20026,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 1393呎 (4+房)
 -
@@ -19926,7 +20040,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>B | 786呎 (3房)
 -
@@ -19934,7 +20048,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 招标单位
@@ -19942,7 +20056,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19951,13 +20065,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>A | 1393呎 (4+房)
 -
@@ -19965,7 +20079,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>B | 786呎 (3房)
 -
@@ -19973,7 +20087,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 招标单位
@@ -19981,7 +20095,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -19990,13 +20104,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>A | 1393呎 (4+房)
 -
@@ -20004,7 +20118,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>B | 786呎 (3房)
 -
@@ -20012,7 +20126,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 招标单位
@@ -20020,7 +20134,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -20029,13 +20143,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="inlineStr">
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>A | 1393呎 (4+房)
 -
@@ -20043,7 +20157,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>B | 786呎 (3房)
 -
@@ -20051,7 +20165,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 招标单位
@@ -20059,7 +20173,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -20068,13 +20182,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>A | 1393呎 (4+房)
 -
@@ -20082,7 +20196,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
         <is>
           <t>B | 786呎 (3房)
 -
@@ -20090,7 +20204,46 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>C | 601呎 (2房)
+$1100万
+$18,296/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>D | 585呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>B | 786呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 招标单位
@@ -20098,7 +20251,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E39" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -20107,13 +20260,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="inlineStr">
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>A | 1393呎 (4+房)
 -
@@ -20121,7 +20274,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
         <is>
           <t>B | 786呎 (3房)
 -
@@ -20129,7 +20282,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D40" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 招标单位
@@ -20137,7 +20290,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -20146,13 +20299,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="inlineStr">
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>A | 1393呎 (4+房)
 -
@@ -20160,7 +20313,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>B | 786呎 (3房)
 -
@@ -20168,7 +20321,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D41" s="22" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
 招标单位
@@ -20176,7 +20329,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E41" s="22" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
 招标单位
@@ -20185,193 +20338,37 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (4+房)
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
-          <t>B | 786呎 (3房)
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>B | 744呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>C | 601呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>D | 585呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (4+房)
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>B | 786呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="inlineStr">
-        <is>
-          <t>C | 601呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E39" s="21" t="inlineStr">
-        <is>
-          <t>D | 585呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C40" s="19" t="inlineStr">
-        <is>
-          <t>B | 786呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t>C | 601呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E40" s="21" t="inlineStr">
-        <is>
-          <t>D | 585呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>B | 786呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D41" s="21" t="inlineStr">
-        <is>
-          <t>C | 601呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E41" s="21" t="inlineStr">
-        <is>
-          <t>D | 585呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>B | 744呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E42" s="19" t="inlineStr">
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>D | 547呎 (2房)
 -
@@ -20405,105 +20402,105 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>1B座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>43&amp;45</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 2847呎 (3房)
 -
@@ -20511,16 +20508,16 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 1744呎 (4+房)
 -
@@ -20528,7 +20525,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 786呎 (3房)
 -
@@ -20536,15 +20533,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20552,7 +20549,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20560,7 +20557,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20570,12 +20567,12 @@
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20583,7 +20580,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20591,7 +20588,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20601,12 +20598,12 @@
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20614,7 +20611,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20622,7 +20619,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20632,12 +20629,12 @@
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20645,7 +20642,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20653,7 +20650,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20663,12 +20660,12 @@
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20676,7 +20673,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20684,7 +20681,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20694,12 +20691,12 @@
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20707,7 +20704,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20715,7 +20712,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20725,12 +20722,12 @@
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20738,7 +20735,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20746,7 +20743,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20756,12 +20753,12 @@
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20769,7 +20766,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20777,7 +20774,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20787,12 +20784,12 @@
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20800,7 +20797,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20808,7 +20805,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20818,12 +20815,12 @@
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20831,7 +20828,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20839,7 +20836,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20849,12 +20846,12 @@
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20862,7 +20859,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20870,7 +20867,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20880,12 +20877,12 @@
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20893,7 +20890,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20901,7 +20898,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20911,12 +20908,12 @@
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20924,7 +20921,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20932,7 +20929,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20942,12 +20939,12 @@
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20955,7 +20952,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20963,7 +20960,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -20973,12 +20970,12 @@
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -20986,7 +20983,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -20994,7 +20991,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -21004,12 +21001,12 @@
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -21017,7 +21014,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -21025,7 +21022,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -21035,12 +21032,12 @@
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -21048,7 +21045,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -21056,7 +21053,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -21066,12 +21063,12 @@
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -21079,7 +21076,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -21087,7 +21084,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -21097,12 +21094,12 @@
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -21110,7 +21107,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -21118,7 +21115,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -21128,12 +21125,12 @@
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 1116呎 (3房)
 -
@@ -21141,7 +21138,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 789呎 (3房)
 -
@@ -21149,7 +21146,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 608呎 (2房)
 -
@@ -21159,12 +21156,12 @@
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21172,7 +21169,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21180,7 +21177,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21190,12 +21187,12 @@
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21203,7 +21200,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21211,7 +21208,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21221,12 +21218,12 @@
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21234,7 +21231,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21242,7 +21239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21252,12 +21249,12 @@
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21265,7 +21262,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21273,7 +21270,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D30" s="19" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21283,12 +21280,12 @@
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21296,7 +21293,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21304,7 +21301,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21314,12 +21311,12 @@
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21327,7 +21324,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21335,7 +21332,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D32" s="19" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21345,12 +21342,12 @@
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B33" s="19" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21358,7 +21355,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21366,7 +21363,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D33" s="19" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21376,12 +21373,12 @@
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21389,7 +21386,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21397,7 +21394,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D34" s="19" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21407,12 +21404,12 @@
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B35" s="19" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21420,7 +21417,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21428,7 +21425,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21438,12 +21435,12 @@
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21451,7 +21448,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21459,7 +21456,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D36" s="19" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21469,12 +21466,12 @@
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B37" s="19" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21482,7 +21479,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21490,7 +21487,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D37" s="19" t="inlineStr">
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21500,12 +21497,12 @@
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B38" s="19" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21513,7 +21510,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C38" s="19" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21521,7 +21518,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D38" s="19" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21531,12 +21528,12 @@
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21544,7 +21541,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21552,7 +21549,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="D39" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21562,12 +21559,12 @@
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B40" s="19" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>A | 1120呎 (3房)
 -
@@ -21575,7 +21572,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C40" s="19" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
         <is>
           <t>B | 788呎 (3房)
 -
@@ -21583,7 +21580,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D40" s="19" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>C | 610呎 (2房)
 -
@@ -21593,12 +21590,12 @@
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B41" s="19" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>A | 1068呎 (3房)
 -
@@ -21606,7 +21603,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C41" s="19" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>B | 746呎 (3房)
 -
@@ -21614,7 +21611,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D41" s="19" t="inlineStr">
+      <c r="D41" s="20" t="inlineStr">
         <is>
           <t>C | 572呎 (2房)
 -

--- a/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
@@ -10202,23 +10202,19 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>10931000</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>18188</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -10227,12 +10223,12 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M138" s="3" t="inlineStr">
@@ -10242,7 +10238,7 @@
       </c>
       <c r="N138" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18858,7 +18854,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18868,7 +18864,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -20243,12 +20239,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr">
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
-招标单位
--
-(在售)</t>
+$1093万
+$18,188/呎
+(26年-09月-20日)</t>
         </is>
       </c>
       <c r="E39" s="22" t="inlineStr">

--- a/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
@@ -7406,23 +7406,19 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>11399000</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>18967</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -7431,12 +7427,12 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
@@ -7446,7 +7442,7 @@
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18854,7 +18850,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18864,7 +18860,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19849,12 +19845,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
-招标单位
--
-(在售)</t>
+$1140万
+$18,967/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">

--- a/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
@@ -6776,23 +6776,19 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>11187000</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>19123</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6801,12 +6797,12 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
@@ -6816,7 +6812,7 @@
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18850,7 +18846,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18860,7 +18856,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19775,12 +19771,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
-招标单位
--
-(在售)</t>
+$1119万
+$19,123/呎
+(26年-09月-25日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
@@ -5100,23 +5100,19 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>11458000</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>19586</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -5125,12 +5121,12 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -5140,7 +5136,7 @@
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18846,7 +18842,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18856,7 +18852,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19537,12 +19533,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
-招标单位
--
-(在售)</t>
+$1146万
+$19,586/呎
+(26年-10月-07日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
@@ -2873,7 +2873,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -19226,7 +19226,7 @@
           <t>D | 585呎 (2房)
 $1259万
 $21,525/呎
-(26年-09月-16日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -19343,7 +19343,7 @@
           <t>D | 585呎 (2房)
 $1211万
 $20,708/呎
-(26年-09月-16日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -19694,7 +19694,7 @@
           <t>D | 585呎 (2房)
 $1128万
 $19,275/呎
-(26年-09月-16日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -20193,7 +20193,7 @@
           <t>C | 601呎 (2房)
 $1100万
 $18,296/呎
-(26年-09月-16日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">

--- a/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
@@ -10195,7 +10195,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -20232,7 +20232,7 @@
           <t>C | 601呎 (2房)
 $1093万
 $18,188/呎
-(26年-09月-20日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E39" s="22" t="inlineStr">

--- a/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第2期/海德园第2期_销控明细表.xlsx
@@ -3424,23 +3424,19 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>12271000</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>20976</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3449,12 +3445,12 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -3464,7 +3460,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5101,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -6282,23 +6278,19 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>11559000</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>19233</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -6307,12 +6299,12 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -6322,7 +6314,7 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6769,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -7403,7 +7395,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -9844,23 +9836,19 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I133" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>10728000</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>18338</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -9869,12 +9857,12 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M133" s="3" t="inlineStr">
@@ -9884,7 +9872,7 @@
       </c>
       <c r="N133" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18842,7 +18830,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18852,7 +18840,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19299,12 +19287,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
-招标单位
--
-(在售)</t>
+$1227万
+$20,976/呎
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -19538,7 +19526,7 @@
           <t>D | 585呎 (2房)
 $1146万
 $19,586/呎
-(26年-10月-07日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -19681,12 +19669,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 601呎 (2房)
-招标单位
--
-(在售)</t>
+$1156万
+$19,233/呎
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -19772,7 +19760,7 @@
           <t>D | 585呎 (2房)
 $1119万
 $19,123/呎
-(26年-09月-25日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -19842,7 +19830,7 @@
           <t>C | 601呎 (2房)
 $1140万
 $18,967/呎
-(26年-09月-22日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -20196,12 +20184,12 @@
 (26年-10月-15日)</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="23" t="inlineStr">
         <is>
           <t>D | 585呎 (2房)
-招标单位
--
-(在售)</t>
+$1073万
+$18,338/呎
+(26年-10月-16日)</t>
         </is>
       </c>
     </row>
